--- a/output/pdf_financials_xlsx/SKK.xlsx
+++ b/output/pdf_financials_xlsx/SKK.xlsx
@@ -2381,46 +2381,46 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.382109</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.382109</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.023998</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.004547</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.009632999999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.020431</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.011913</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.035817</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.10187</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.173276</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.101137</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.225913</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.475178</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.511719</v>
       </c>
       <c r="Q34" s="1" t="inlineStr">
         <is>
@@ -2509,46 +2509,46 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.382109</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.382109</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.023998</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.004547</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.009632999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.020431</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.011913</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.035817</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.10187</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.173276</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.101137</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.225913</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.475178</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.511719</v>
       </c>
       <c r="Q36" s="1" t="inlineStr">
         <is>
@@ -3280,43 +3280,43 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.382109</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.023998</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.004547</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.009632999999999999</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.020431</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.011913</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.035817</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.10187</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.173276</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.101137</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.232888</v>
+        <v>0.006975</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.480178</v>
+        <v>0.005</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.516719</v>
+        <v>0.005</v>
       </c>
       <c r="Q48" s="1" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">

--- a/output/pdf_financials_xlsx/SKK.xlsx
+++ b/output/pdf_financials_xlsx/SKK.xlsx
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.508142</v>
+        <v>0.552176</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.765929</v>
+        <v>-0.755007</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.765929</v>
+        <v>-1.531858</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.984113</v>
@@ -1311,7 +1311,7 @@
         <v>-2.057179</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.95261</v>
+        <v>-3.90522</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-1.59573</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.044034</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.010922</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.765929</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1371,7 +1371,7 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>1.95261</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0.106366</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.508142</v>
+        <v>0.552176</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.765929</v>
+        <v>-0.755007</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.765929</v>
+        <v>-1.531858</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.984113</v>
@@ -2035,7 +2035,7 @@
         <v>-2.057179</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.95261</v>
+        <v>-3.90522</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-1.59573</v>
@@ -2134,13 +2134,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.508142</v>
+        <v>0.552176</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.765929</v>
+        <v>-0.755007</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.765929</v>
+        <v>-1.531858</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.984113</v>
@@ -2155,7 +2155,7 @@
         <v>-2.057179</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.95261</v>
+        <v>-3.90522</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-1.59573</v>
@@ -2194,13 +2194,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>93.69177015054714</v>
+        <v>101.8108065750293</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-630.4461272532719</v>
+        <v>-621.4560869207343</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-442.6746733093288</v>
+        <v>-885.3493466186576</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-1237.862416824946</v>
@@ -2215,7 +2215,7 @@
         <v>-669.6023097153868</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-356.2695344216352</v>
+        <v>-712.5390688432703</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>-272.8984461310613</v>
@@ -2254,13 +2254,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>7.97463127698415</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.44660910428645</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-50</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -2275,7 +2275,7 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-50</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-6.665663990775382</v>
@@ -4533,50 +4533,46 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0325</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.036467</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.026859</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0265</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.0275</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.0275</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.02875</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.0335</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.035987</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03375</v>
+      </c>
+      <c r="Q67" s="3" t="n">
+        <v>0.03763</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>0.051051</v>
       </c>
     </row>
     <row r="68">
@@ -32799,7 +32795,11 @@
           <t>Loss before income tax recovery</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -33904,7 +33904,11 @@
           <t>Income (loss) before income tax recovery</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -34003,7 +34007,11 @@
           <t>Income tax recovery 13</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -39611,7 +39619,11 @@
           <t>Loss before other item and income tax recovery</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -39811,7 +39823,11 @@
           <t>Income (loss) before income tax recovery</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -39910,7 +39926,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -42730,7 +42750,11 @@
           <t>Income Before Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -42829,7 +42853,11 @@
           <t>Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
